--- a/outputs/Ket_Qua_Xep_Lich.xlsx
+++ b/outputs/Ket_Qua_Xep_Lich.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CB009, CB038, CB011, CB022</t>
+          <t>CB018, CB038, CB011, CB042</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CB007, CB027, CB046, CB049</t>
+          <t>CB030, CB061, CB067, CB001</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CB014</t>
+          <t>CB016</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CB004, CB034, CB025, CB038, CB042, CB020, CB026, CB010, CB033, CB046, CB067, CB012, CB014, CB055, CB024, CB059, CB072, CB028, CB047, CB040, CB057, CB053, CB041, CB003, CB045, CB065, CB061, CB032, CB048, CB066, CB039, CB051</t>
+          <t>CB004, CB013, CB069, CB038, CB042, CB020, CB026, CB010, CB062, CB046, CB067, CB012, CB006, CB055, CB024, CB059, CB072, CB028, CB047, CB027, CB057, CB053, CB041, CB003, CB045, CB065, CB014, CB032, CB048, CB066, CB039, CB051</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CB012, CB037, CB069, CB032, CB071, CB015, CB062, CB005, CB063, CB030, CB011, CB014, CB049, CB060, CB019, CB035, CB016, CB001, CB073, CB007, CB022, CB051, CB052, CB050, CB017, CB013, CB068, CB064</t>
+          <t>CB012, CB037, CB069, CB032, CB071, CB015, CB062, CB021, CB063, CB030, CB011, CB054, CB049, CB060, CB019, CB035, CB016, CB001, CB031, CB007, CB022, CB051, CB052, CB041, CB017, CB039, CB003, CB056</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CB020</t>
+          <t>CB003</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CB054</t>
+          <t>CB068</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CB030, CB058, CB039, CB048, CB041, CB033, CB057, CB001, CB038, CB025, CB061, CB029, CB008, CB034, CB013, CB062, CB036, CB069, CB064, CB053, CB015, CB022, CB012, CB005, CB070, CB059, CB023, CB047, CB045, CB035</t>
+          <t>CB030, CB058, CB039, CB048, CB041, CB033, CB019, CB004, CB038, CB025, CB061, CB029, CB043, CB056, CB002, CB054, CB036, CB069, CB064, CB053, CB015, CB040, CB012, CB005, CB070, CB059, CB023, CB016, CB045, CB035</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CB052, CB011, CB065</t>
+          <t>CB060, CB011, CB065</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CB032, CB006, CB055, CB033, CB063, CB035, CB019, CB071, CB028, CB009, CB031, CB010, CB067, CB042, CB018, CB073, CB016, CB026, CB027, CB054, CB013, CB072, CB020, CB066, CB040, CB058, CB056, CB001, CB017, CB043</t>
+          <t>CB032, CB006, CB055, CB033, CB063, CB036, CB012, CB071, CB028, CB009, CB031, CB010, CB007, CB042, CB008, CB073, CB016, CB026, CB027, CB002, CB013, CB072, CB051, CB066, CB021, CB058, CB056, CB001, CB017, CB043</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CB044, CB003, CB024</t>
+          <t>CB044, CB037, CB024</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CB020, CB037, CB029, CB068</t>
+          <t>CB020, CB034, CB029, CB068</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CB060, CB004, CB049</t>
+          <t>CB057, CB046, CB049</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CB051, CB055</t>
+          <t>CB053, CB055</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CB041, CB061, CB018, CB025, CB008, CB058, CB003, CB065, CB033, CB026, CB052, CB050, CB057, CB043, CB053, CB032, CB038</t>
+          <t>CB022, CB061, CB018, CB025, CB008, CB058, CB040, CB065, CB035, CB026, CB052, CB050, CB059, CB043, CB055, CB032, CB068</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CB015, CB067, CB066</t>
+          <t>CB015, CB037, CB066</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CB013</t>
+          <t>CB009</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CB019, CB008, CB022, CB028, CB063, CB011, CB002, CB026, CB060, CB065, CB020, CB007, CB024, CB073, CB067, CB010, CB032, CB045, CB051, CB023, CB050, CB056, CB034, CB055, CB044, CB066, CB031, CB071, CB003, CB043, CB018, CB048</t>
+          <t>CB014, CB013, CB022, CB029, CB063, CB011, CB002, CB026, CB060, CB038, CB020, CB007, CB024, CB005, CB067, CB010, CB025, CB054, CB035, CB023, CB050, CB056, CB034, CB055, CB036, CB066, CB031, CB071, CB003, CB043, CB018, CB048</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CB004, CB012, CB014, CB053, CB054, CB052, CB011, CB048, CB028, CB057, CB071, CB045, CB030, CB033, CB002, CB016, CB001, CB064, CB041, CB034, CB069, CB025, CB058, CB029, CB061, CB027, CB005, CB021, CB017, CB009, CB042, CB068</t>
+          <t>CB004, CB012, CB065, CB053, CB054, CB052, CB011, CB019, CB028, CB059, CB071, CB046, CB030, CB033, CB049, CB016, CB036, CB072, CB041, CB034, CB015, CB025, CB051, CB010, CB061, CB027, CB005, CB021, CB017, CB035, CB042, CB068</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CB029, CB003, CB020, CB047, CB023, CB026, CB073, CB027, CB070, CB004, CB039, CB012, CB035, CB067, CB066</t>
+          <t>CB029, CB002, CB020, CB004, CB023, CB026, CB070, CB069, CB060, CB068, CB046, CB010, CB047, CB067, CB066</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CB036, CB037</t>
+          <t>CB032, CB044</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CB038, CB050, CB065, CB037, CB028, CB070, CB011, CB056, CB013, CB068, CB059, CB029, CB058, CB061, CB069, CB023, CB027, CB012, CB034, CB040</t>
+          <t>CB006, CB050, CB065, CB037, CB028, CB070, CB011, CB069, CB013, CB067, CB059, CB029, CB058, CB061, CB047, CB023, CB027, CB012, CB042, CB040</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CB031, CB003, CB019, CB017, CB072, CB045, CB063, CB014, CB021, CB007, CB067, CB054, CB047, CB036, CB050</t>
+          <t>CB031, CB003, CB019, CB017, CB066, CB045, CB063, CB014, CB055, CB007, CB068, CB054, CB064, CB036, CB050</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CB052</t>
+          <t>CB061</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CB004, CB010, CB012</t>
+          <t>CB046, CB023, CB012</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CB020, CB055</t>
+          <t>CB020, CB025</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CB051, CB067, CB070, CB047, CB009, CB003, CB030, CB044, CB032, CB058, CB001, CB040, CB071, CB033, CB004, CB007, CB066, CB056, CB054, CB068, CB064, CB060, CB035, CB050, CB059, CB008, CB038, CB019, CB005, CB046, CB006</t>
+          <t>CB051, CB067, CB070, CB047, CB009, CB003, CB030, CB044, CB032, CB058, CB002, CB040, CB071, CB033, CB004, CB007, CB066, CB056, CB054, CB068, CB064, CB055, CB035, CB050, CB059, CB060, CB037, CB019, CB023, CB046, CB043</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CB041, CB034, CB059, CB062, CB049, CB013, CB024, CB001, CB055, CB015, CB039, CB048, CB042, CB025, CB017, CB044, CB023, CB052, CB065, CB022, CB057, CB037, CB036, CB063, CB073, CB006, CB061, CB043, CB029, CB072, CB002</t>
+          <t>CB041, CB034, CB059, CB062, CB049, CB013, CB008, CB001, CB031, CB015, CB050, CB048, CB042, CB025, CB017, CB044, CB023, CB052, CB065, CB069, CB057, CB022, CB036, CB063, CB073, CB006, CB011, CB027, CB029, CB072, CB002</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CB066, CB047, CB068, CB018, CB045, CB063, CB004, CB064, CB008, CB014, CB016, CB046, CB053, CB026, CB035, CB048, CB070, CB049, CB069, CB010, CB013, CB020, CB030, CB005, CB034, CB058, CB022, CB031, CB019, CB040, CB038</t>
+          <t>CB066, CB047, CB068, CB018, CB052, CB061, CB004, CB064, CB008, CB014, CB016, CB060, CB053, CB026, CB035, CB048, CB070, CB027, CB069, CB010, CB013, CB020, CB030, CB042, CB034, CB058, CB022, CB031, CB019, CB040, CB039</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CB004, CB041, CB011, CB012, CB024, CB025, CB042, CB067, CB023, CB027, CB002, CB057, CB071, CB055, CB037, CB026, CB060, CB003, CB001, CB009, CB034</t>
+          <t>CB003, CB041, CB011, CB017, CB034, CB025, CB035, CB067, CB049, CB063, CB005, CB057, CB071, CB055, CB037, CB026, CB060, CB039, CB001, CB009, CB073</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CB056</t>
+          <t>CB038</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CB055</t>
+          <t>CB045</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CB036, CB072, CB001, CB040, CB015</t>
+          <t>CB036, CB072, CB009, CB040, CB047</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CB058, CB021, CB037, CB013, CB026, CB016, CB048, CB045, CB033, CB007, CB065, CB008, CB051, CB006, CB041, CB028, CB060, CB053, CB003, CB070, CB066, CB042, CB044, CB020, CB018, CB014, CB034, CB035, CB054, CB062</t>
+          <t>CB023, CB073, CB037, CB011, CB005, CB063, CB048, CB045, CB033, CB007, CB065, CB008, CB022, CB006, CB046, CB028, CB060, CB053, CB049, CB070, CB066, CB029, CB044, CB020, CB018, CB014, CB034, CB059, CB031, CB062</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CB009</t>
+          <t>CB019</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CB036, CB060</t>
+          <t>CB036, CB042</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CB002, CB015, CB064, CB042, CB032, CB061, CB060, CB017, CB047, CB024</t>
+          <t>CB002, CB048, CB053, CB033, CB026, CB073, CB060, CB017, CB047, CB024</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CB016, CB031, CB025, CB070, CB071, CB010, CB063</t>
+          <t>CB016, CB045, CB027, CB070, CB071, CB014, CB063</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CB021, CB055, CB035, CB059</t>
+          <t>CB021, CB009, CB035, CB061</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CB030, CB033</t>
+          <t>CB032, CB033</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CB021, CB055, CB061, CB009, CB001, CB065, CB030, CB072, CB064, CB028, CB044, CB005, CB015, CB046, CB026, CB050, CB073, CB043, CB022, CB004, CB025, CB045, CB063, CB049, CB056, CB008, CB062, CB068, CB039</t>
+          <t>CB021, CB054, CB027, CB009, CB001, CB065, CB030, CB072, CB064, CB028, CB063, CB005, CB015, CB051, CB070, CB047, CB073, CB043, CB022, CB004, CB025, CB018, CB060, CB049, CB056, CB008, CB062, CB058, CB039</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CB047</t>
+          <t>CB055</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CB012</t>
+          <t>CB056</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CB061</t>
+          <t>CB004</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CB068, CB005, CB018, CB027, CB072, CB059, CB008, CB066, CB021, CB006, CB069, CB050, CB032, CB058</t>
+          <t>CB037, CB005, CB018, CB008, CB045, CB049, CB028, CB030, CB021, CB001, CB069, CB050, CB032, CB044</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CB002</t>
+          <t>CB012</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CB019, CB070, CB073</t>
+          <t>CB015, CB022, CB073</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CB072, CB070, CB006, CB005, CB049, CB015, CB048, CB012, CB016, CB028, CB039, CB046, CB002, CB073, CB054, CB053, CB065, CB010, CB037, CB027, CB056, CB019</t>
+          <t>CB072, CB071, CB006, CB005, CB049, CB021, CB001, CB012, CB016, CB028, CB039, CB046, CB058, CB073, CB032, CB053, CB065, CB010, CB037, CB051, CB056, CB003</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CB043, CB024, CB021, CB003, CB057, CB034, CB031, CB035, CB007, CB018, CB038, CB017, CB004, CB041, CB063, CB028, CB042, CB071, CB036, CB005, CB070, CB023, CB051, CB020, CB062, CB061, CB030, CB026, CB001, CB067</t>
+          <t>CB040, CB024, CB021, CB003, CB057, CB050, CB058, CB035, CB007, CB018, CB038, CB017, CB004, CB041, CB063, CB028, CB044, CB013, CB046, CB073, CB070, CB033, CB047, CB020, CB062, CB061, CB019, CB026, CB006, CB067</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CB029, CB044, CB068, CB073, CB037</t>
+          <t>CB023, CB051, CB068, CB073, CB036</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CB005, CB051, CB022, CB036, CB016, CB071, CB018, CB037, CB054, CB056, CB013, CB006, CB068, CB017, CB030, CB049, CB043, CB047, CB064, CB033, CB057, CB050, CB069, CB062, CB026, CB052, CB039, CB021, CB040, CB020, CB007, CB041</t>
+          <t>CB005, CB051, CB038, CB036, CB016, CB071, CB001, CB037, CB054, CB056, CB020, CB006, CB068, CB024, CB030, CB049, CB043, CB047, CB064, CB033, CB057, CB055, CB048, CB062, CB026, CB052, CB014, CB021, CB040, CB015, CB008, CB041</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CB031, CB040, CB002, CB058, CB072, CB067</t>
+          <t>CB007, CB040, CB002, CB058, CB072, CB017</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CB001, CB035, CB059, CB027, CB054, CB021, CB055, CB051, CB017, CB018, CB028, CB049, CB065, CB069, CB039, CB011, CB033, CB014, CB071, CB009, CB057, CB046, CB030, CB063, CB006, CB019, CB023, CB029, CB066, CB026, CB064</t>
+          <t>CB001, CB035, CB059, CB027, CB054, CB021, CB055, CB051, CB017, CB018, CB028, CB049, CB070, CB069, CB031, CB011, CB033, CB014, CB071, CB009, CB057, CB046, CB030, CB063, CB006, CB019, CB023, CB029, CB065, CB026, CB064</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CB044, CB042, CB048, CB073, CB071, CB001, CB012, CB041, CB037, CB054, CB034, CB067, CB020, CB046, CB036, CB003, CB024, CB029, CB015, CB043, CB031</t>
+          <t>CB044, CB042, CB048, CB073, CB071, CB052, CB012, CB009, CB037, CB054, CB034, CB067, CB020, CB046, CB036, CB066, CB041, CB029, CB015, CB043, CB032</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CB004</t>
+          <t>CB013</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CB070, CB011</t>
+          <t>CB070, CB020</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CB047, CB027, CB051, CB045, CB011, CB043, CB036, CB010, CB019, CB022, CB038, CB053, CB016, CB024, CB049, CB004, CB057, CB013, CB059, CB056, CB055, CB064, CB063, CB018, CB015, CB008, CB017, CB006, CB062, CB060, CB044</t>
+          <t>CB047, CB027, CB051, CB045, CB039, CB043, CB003, CB010, CB013, CB022, CB038, CB053, CB016, CB024, CB049, CB004, CB050, CB012, CB059, CB046, CB055, CB064, CB009, CB018, CB015, CB008, CB067, CB026, CB062, CB060, CB044</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CB023</t>
+          <t>CB072</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CB021</t>
+          <t>CB005</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CB061, CB009, CB002</t>
+          <t>CB063, CB057, CB005</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CB025, CB015, CB039, CB052, CB046, CB014</t>
+          <t>CB025, CB015, CB039, CB052, CB044, CB013</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CB064, CB062, CB042, CB006, CB051, CB022</t>
+          <t>CB064, CB062, CB042, CB006, CB019, CB022</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CB054, CB019, CB027, CB029</t>
+          <t>CB045, CB014, CB029, CB004</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CB002, CB007, CB010, CB044, CB060, CB046</t>
+          <t>CB002, CB007, CB010, CB044, CB060, CB027</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CB053, CB031, CB072, CB039, CB059, CB040</t>
+          <t>CB038, CB031, CB034, CB057, CB072, CB024</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CB016, CB023, CB032, CB045</t>
+          <t>CB029, CB008, CB064, CB045</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CB069, CB048, CB008, CB002</t>
+          <t>CB069, CB048, CB024, CB002</t>
         </is>
       </c>
     </row>
@@ -3821,11 +3821,11 @@
         <v>4.4</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3850,11 +3850,11 @@
         <v>21.4</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>6.3</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3908,11 +3908,11 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3937,11 +3937,11 @@
         <v>7.9</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4053,11 +4053,11 @@
         <v>2.1</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4343,11 +4343,11 @@
         <v>17.7</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4372,11 +4372,11 @@
         <v>14.3</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4633,11 +4633,11 @@
         <v>6.9</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4720,11 +4720,11 @@
         <v>11.7</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4778,11 +4778,11 @@
         <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4807,11 +4807,11 @@
         <v>12.1</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4836,11 +4836,11 @@
         <v>5.8</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4923,11 +4923,11 @@
         <v>16.7</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4981,11 +4981,11 @@
         <v>5.1</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5068,11 +5068,11 @@
         <v>23.4</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5126,11 +5126,11 @@
         <v>2.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5155,11 +5155,11 @@
         <v>23.3</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5213,11 +5213,11 @@
         <v>23.7</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5358,11 +5358,11 @@
         <v>16</v>
       </c>
       <c r="F55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5445,11 +5445,11 @@
         <v>5.7</v>
       </c>
       <c r="F58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5532,11 +5532,11 @@
         <v>10.3</v>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5561,11 +5561,11 @@
         <v>8.9</v>
       </c>
       <c r="F62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5619,11 +5619,11 @@
         <v>23.3</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5648,11 +5648,11 @@
         <v>16.5</v>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5735,11 +5735,11 @@
         <v>9.5</v>
       </c>
       <c r="F68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5793,11 +5793,11 @@
         <v>22.7</v>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5909,11 +5909,11 @@
         <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6841</v>
+        <v>0.7038</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Ket_Qua_Xep_Lich.xlsx
+++ b/outputs/Ket_Qua_Xep_Lich.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CB018, CB038, CB011, CB042</t>
+          <t>CB014, CB038, CB011, CB072</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CB030, CB061, CB067, CB001</t>
+          <t>CB007, CB061, CB046, CB001</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CB016</t>
+          <t>CB071</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CB004, CB013, CB069, CB038, CB042, CB020, CB026, CB010, CB062, CB046, CB067, CB012, CB006, CB055, CB024, CB059, CB072, CB028, CB047, CB027, CB057, CB053, CB041, CB003, CB045, CB065, CB014, CB032, CB048, CB066, CB039, CB051</t>
+          <t>CB004, CB064, CB025, CB038, CB042, CB050, CB026, CB010, CB033, CB046, CB067, CB018, CB073, CB055, CB024, CB059, CB072, CB028, CB047, CB006, CB057, CB053, CB041, CB003, CB045, CB065, CB061, CB032, CB048, CB066, CB039, CB008</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CB012, CB037, CB069, CB032, CB071, CB015, CB062, CB021, CB063, CB030, CB011, CB054, CB049, CB060, CB019, CB035, CB016, CB001, CB031, CB007, CB022, CB051, CB052, CB041, CB017, CB039, CB003, CB056</t>
+          <t>CB012, CB037, CB069, CB031, CB071, CB015, CB062, CB005, CB063, CB030, CB011, CB054, CB049, CB060, CB019, CB035, CB016, CB001, CB072, CB007, CB022, CB051, CB052, CB042, CB017, CB013, CB065, CB066</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CB003</t>
+          <t>CB020</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CB007, CB014</t>
+          <t>CB007, CB018</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CB030, CB058, CB039, CB048, CB041, CB033, CB019, CB004, CB038, CB025, CB061, CB029, CB043, CB056, CB002, CB054, CB036, CB069, CB064, CB053, CB015, CB040, CB012, CB005, CB070, CB059, CB023, CB016, CB045, CB035</t>
+          <t>CB030, CB058, CB039, CB048, CB041, CB033, CB057, CB001, CB038, CB025, CB061, CB029, CB008, CB034, CB002, CB054, CB036, CB069, CB064, CB053, CB015, CB022, CB012, CB005, CB070, CB059, CB023, CB016, CB045, CB035</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CB032, CB006, CB055, CB033, CB063, CB036, CB012, CB071, CB028, CB009, CB031, CB010, CB007, CB042, CB008, CB073, CB016, CB026, CB027, CB002, CB013, CB072, CB051, CB066, CB021, CB058, CB056, CB001, CB017, CB043</t>
+          <t>CB032, CB006, CB055, CB033, CB063, CB035, CB019, CB052, CB028, CB009, CB031, CB010, CB067, CB042, CB014, CB073, CB016, CB026, CB027, CB002, CB013, CB037, CB051, CB072, CB021, CB058, CB056, CB001, CB017, CB043</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CB044, CB037, CB024</t>
+          <t>CB044, CB003, CB024</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CB057, CB046, CB049</t>
+          <t>CB060, CB065, CB049</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CB053, CB055</t>
+          <t>CB049, CB063</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CB022, CB061, CB018, CB025, CB008, CB058, CB040, CB065, CB035, CB026, CB052, CB050, CB059, CB043, CB055, CB032, CB068</t>
+          <t>CB041, CB061, CB018, CB056, CB067, CB058, CB040, CB065, CB035, CB026, CB052, CB050, CB057, CB043, CB055, CB032, CB006</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CB015, CB037, CB066</t>
+          <t>CB046, CB033, CB066</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CB009</t>
+          <t>CB013</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CB014, CB013, CB022, CB029, CB063, CB011, CB002, CB026, CB060, CB038, CB020, CB007, CB024, CB005, CB067, CB010, CB025, CB054, CB035, CB023, CB050, CB056, CB034, CB055, CB036, CB066, CB031, CB071, CB003, CB043, CB018, CB048</t>
+          <t>CB019, CB008, CB022, CB029, CB063, CB069, CB002, CB026, CB060, CB065, CB020, CB007, CB024, CB073, CB067, CB010, CB032, CB054, CB051, CB023, CB050, CB056, CB034, CB055, CB040, CB066, CB031, CB059, CB003, CB043, CB018, CB004</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CB004, CB012, CB065, CB053, CB054, CB052, CB011, CB019, CB028, CB059, CB071, CB046, CB030, CB033, CB049, CB016, CB036, CB072, CB041, CB034, CB015, CB025, CB051, CB010, CB061, CB027, CB005, CB021, CB017, CB035, CB042, CB068</t>
+          <t>CB004, CB012, CB014, CB053, CB070, CB015, CB011, CB048, CB028, CB057, CB071, CB046, CB030, CB033, CB047, CB016, CB036, CB072, CB041, CB034, CB020, CB025, CB051, CB010, CB061, CB027, CB005, CB021, CB017, CB035, CB042, CB068</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CB029, CB002, CB020, CB004, CB023, CB026, CB070, CB069, CB060, CB068, CB046, CB010, CB047, CB067, CB066</t>
+          <t>CB029, CB003, CB009, CB052, CB023, CB026, CB054, CB058, CB060, CB013, CB032, CB012, CB044, CB067, CB066</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CB032, CB044</t>
+          <t>CB036, CB037</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CB024, CB005, CB039, CB062, CB032</t>
+          <t>CB002, CB025, CB016, CB062, CB032</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CB006, CB050, CB065, CB037, CB028, CB070, CB011, CB069, CB013, CB067, CB059, CB029, CB058, CB061, CB047, CB023, CB027, CB012, CB042, CB040</t>
+          <t>CB006, CB050, CB052, CB037, CB028, CB070, CB009, CB056, CB013, CB071, CB059, CB029, CB066, CB060, CB047, CB023, CB027, CB012, CB042, CB040</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CB031, CB003, CB019, CB017, CB066, CB045, CB063, CB014, CB055, CB007, CB068, CB054, CB064, CB036, CB050</t>
+          <t>CB031, CB003, CB019, CB017, CB072, CB045, CB063, CB014, CB055, CB007, CB068, CB054, CB058, CB036, CB035</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CB061</t>
+          <t>CB057</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CB046, CB023, CB012</t>
+          <t>CB004, CB023, CB012</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CB020, CB025</t>
+          <t>CB020, CB051</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CB051, CB067, CB070, CB047, CB009, CB003, CB030, CB044, CB032, CB058, CB002, CB040, CB071, CB033, CB004, CB007, CB066, CB056, CB054, CB068, CB064, CB055, CB035, CB050, CB059, CB060, CB037, CB019, CB023, CB046, CB043</t>
+          <t>CB051, CB067, CB070, CB047, CB009, CB008, CB026, CB043, CB018, CB058, CB052, CB040, CB071, CB033, CB053, CB007, CB066, CB056, CB039, CB068, CB064, CB055, CB035, CB050, CB059, CB060, CB038, CB045, CB005, CB046, CB014</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CB041, CB034, CB059, CB062, CB049, CB013, CB008, CB001, CB031, CB015, CB050, CB048, CB042, CB025, CB017, CB044, CB023, CB052, CB065, CB069, CB057, CB022, CB036, CB063, CB073, CB006, CB011, CB027, CB029, CB072, CB002</t>
+          <t>CB041, CB034, CB059, CB062, CB049, CB013, CB024, CB067, CB031, CB015, CB050, CB048, CB042, CB025, CB017, CB044, CB023, CB054, CB065, CB069, CB057, CB022, CB032, CB063, CB073, CB006, CB011, CB030, CB029, CB072, CB002</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CB066, CB047, CB068, CB018, CB052, CB061, CB004, CB064, CB008, CB014, CB016, CB060, CB053, CB026, CB035, CB048, CB070, CB027, CB069, CB010, CB013, CB020, CB030, CB042, CB034, CB058, CB022, CB031, CB019, CB040, CB039</t>
+          <t>CB066, CB047, CB068, CB018, CB052, CB061, CB004, CB057, CB008, CB014, CB016, CB060, CB053, CB026, CB035, CB051, CB070, CB049, CB003, CB010, CB013, CB020, CB036, CB042, CB028, CB058, CB022, CB031, CB019, CB040, CB038</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CB003, CB041, CB011, CB017, CB034, CB025, CB035, CB067, CB049, CB063, CB005, CB057, CB071, CB055, CB037, CB026, CB060, CB039, CB001, CB009, CB073</t>
+          <t>CB004, CB041, CB011, CB017, CB015, CB025, CB045, CB067, CB021, CB027, CB005, CB002, CB071, CB055, CB037, CB029, CB054, CB039, CB001, CB009, CB024</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CB038</t>
+          <t>CB071</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CB045</t>
+          <t>CB055</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CB061</t>
+          <t>CB012</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CB036, CB072, CB009, CB040, CB047</t>
+          <t>CB036, CB072, CB001, CB040, CB039</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CB023, CB073, CB037, CB011, CB005, CB063, CB048, CB045, CB033, CB007, CB065, CB008, CB022, CB006, CB046, CB028, CB060, CB053, CB049, CB070, CB066, CB029, CB044, CB020, CB018, CB014, CB034, CB059, CB031, CB062</t>
+          <t>CB058, CB021, CB037, CB011, CB026, CB063, CB048, CB045, CB033, CB007, CB065, CB008, CB051, CB006, CB046, CB028, CB056, CB053, CB003, CB070, CB064, CB029, CB044, CB020, CB018, CB014, CB034, CB059, CB054, CB062</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CB019</t>
+          <t>CB017</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CB036, CB042</t>
+          <t>CB037, CB047</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CB047</t>
+          <t>CB049</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CB002, CB048, CB053, CB033, CB026, CB073, CB060, CB017, CB047, CB024</t>
+          <t>CB002, CB009, CB021, CB042, CB032, CB043, CB069, CB020, CB047, CB006</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CB016, CB045, CB027, CB070, CB071, CB014, CB063</t>
+          <t>CB016, CB031, CB027, CB070, CB071, CB010, CB063</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CB021, CB009, CB035, CB061</t>
+          <t>CB019, CB038, CB035, CB059</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CB032, CB033</t>
+          <t>CB030, CB036</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CB021, CB054, CB027, CB009, CB001, CB065, CB030, CB072, CB064, CB028, CB063, CB005, CB015, CB051, CB070, CB047, CB073, CB043, CB022, CB004, CB025, CB018, CB060, CB049, CB056, CB008, CB062, CB058, CB039</t>
+          <t>CB021, CB059, CB027, CB009, CB001, CB065, CB030, CB072, CB064, CB032, CB063, CB005, CB015, CB051, CB026, CB041, CB073, CB043, CB022, CB004, CB025, CB018, CB060, CB050, CB056, CB008, CB062, CB068, CB039</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CB036, CB009</t>
+          <t>CB073, CB009</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CB056</t>
+          <t>CB021</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CB004</t>
+          <t>CB061</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CB037, CB005, CB018, CB008, CB045, CB049, CB028, CB030, CB021, CB001, CB069, CB050, CB032, CB044</t>
+          <t>CB068, CB062, CB036, CB002, CB070, CB049, CB016, CB030, CB021, CB001, CB069, CB050, CB032, CB044</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CB012</t>
+          <t>CB007</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CB015, CB022, CB073</t>
+          <t>CB011, CB022, CB073</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CB072, CB071, CB006, CB005, CB049, CB021, CB001, CB012, CB016, CB028, CB039, CB046, CB058, CB073, CB032, CB053, CB065, CB010, CB037, CB051, CB056, CB003</t>
+          <t>CB072, CB070, CB031, CB030, CB049, CB015, CB048, CB012, CB016, CB028, CB039, CB046, CB002, CB073, CB043, CB053, CB065, CB036, CB037, CB051, CB056, CB019</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CB040, CB024, CB021, CB003, CB057, CB050, CB058, CB035, CB007, CB018, CB038, CB017, CB004, CB041, CB063, CB028, CB044, CB013, CB046, CB073, CB070, CB033, CB047, CB020, CB062, CB061, CB019, CB026, CB006, CB067</t>
+          <t>CB040, CB024, CB025, CB003, CB057, CB050, CB058, CB035, CB007, CB018, CB014, CB017, CB004, CB041, CB063, CB028, CB044, CB071, CB066, CB005, CB070, CB023, CB047, CB020, CB054, CB061, CB019, CB068, CB001, CB062</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CB023, CB051, CB068, CB073, CB036</t>
+          <t>CB037, CB049, CB029, CB073, CB036</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CB005, CB051, CB038, CB036, CB016, CB071, CB001, CB037, CB054, CB056, CB020, CB006, CB068, CB024, CB030, CB049, CB043, CB047, CB064, CB033, CB057, CB055, CB048, CB062, CB026, CB052, CB014, CB021, CB040, CB015, CB008, CB041</t>
+          <t>CB005, CB051, CB038, CB036, CB017, CB071, CB018, CB037, CB054, CB056, CB013, CB006, CB068, CB024, CB030, CB049, CB043, CB011, CB064, CB060, CB053, CB055, CB048, CB062, CB026, CB045, CB039, CB021, CB040, CB020, CB008, CB041</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CB007, CB040, CB002, CB058, CB072, CB017</t>
+          <t>CB012, CB040, CB044, CB058, CB015, CB065</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CB001, CB035, CB059, CB027, CB054, CB021, CB055, CB051, CB017, CB018, CB028, CB049, CB070, CB069, CB031, CB011, CB033, CB014, CB071, CB009, CB057, CB046, CB030, CB063, CB006, CB019, CB023, CB029, CB065, CB026, CB064</t>
+          <t>CB001, CB035, CB059, CB027, CB053, CB021, CB055, CB061, CB017, CB038, CB028, CB049, CB005, CB069, CB031, CB011, CB033, CB014, CB003, CB009, CB057, CB046, CB037, CB063, CB006, CB019, CB023, CB030, CB066, CB026, CB064</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CB010, CB025</t>
+          <t>CB004, CB025</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CB044, CB042, CB048, CB073, CB071, CB052, CB012, CB009, CB037, CB054, CB034, CB067, CB020, CB046, CB036, CB066, CB041, CB029, CB015, CB043, CB032</t>
+          <t>CB044, CB042, CB048, CB073, CB071, CB052, CB012, CB009, CB037, CB054, CB034, CB067, CB020, CB046, CB036, CB008, CB024, CB029, CB015, CB039, CB032</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CB013</t>
+          <t>CB010</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CB070, CB020</t>
+          <t>CB070, CB013</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CB047, CB027, CB051, CB045, CB039, CB043, CB003, CB010, CB013, CB022, CB038, CB053, CB016, CB024, CB049, CB004, CB050, CB012, CB059, CB046, CB055, CB064, CB009, CB018, CB015, CB008, CB067, CB026, CB062, CB060, CB044</t>
+          <t>CB047, CB027, CB051, CB045, CB011, CB043, CB003, CB010, CB013, CB022, CB038, CB053, CB016, CB024, CB049, CB004, CB069, CB012, CB059, CB046, CB055, CB064, CB063, CB018, CB015, CB061, CB067, CB026, CB062, CB060, CB044</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CB072</t>
+          <t>CB023</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CB063, CB057, CB005</t>
+          <t>CB054, CB009, CB005</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CB031, CB057, CB040, CB053</t>
+          <t>CB031, CB057, CB040, CB047</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CB025, CB015, CB039, CB052, CB044, CB013</t>
+          <t>CB025, CB015, CB039, CB052, CB033, CB010</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CB041, CB069, CB024, CB038</t>
+          <t>CB041, CB069, CB034, CB038</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CB045, CB014, CB029, CB004</t>
+          <t>CB045, CB014, CB028, CB029</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CB002, CB007, CB010, CB044, CB060, CB027</t>
+          <t>CB002, CB007, CB010, CB044, CB048, CB027</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CB038, CB031, CB034, CB057, CB072, CB024</t>
+          <t>CB033, CB004, CB022, CB027, CB073, CB024</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CB029, CB008, CB064, CB045</t>
+          <t>CB034, CB023, CB064, CB045</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CB069, CB048, CB024, CB002</t>
+          <t>CB069, CB048, CB008, CB002</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3850,11 +3850,11 @@
         <v>21.4</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3937,11 +3937,11 @@
         <v>7.9</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4111,11 +4111,11 @@
         <v>24.4</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4314,11 +4314,11 @@
         <v>1.9</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4488,11 +4488,11 @@
         <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4575,11 +4575,11 @@
         <v>10.6</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5068,11 +5068,11 @@
         <v>23.4</v>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5126,11 +5126,11 @@
         <v>2.6</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5155,11 +5155,11 @@
         <v>23.3</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5271,11 +5271,11 @@
         <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5300,11 +5300,11 @@
         <v>24.7</v>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5358,11 +5358,11 @@
         <v>16</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5503,11 +5503,11 @@
         <v>24.8</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5532,11 +5532,11 @@
         <v>10.3</v>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5677,11 +5677,11 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5793,11 +5793,11 @@
         <v>22.7</v>
       </c>
       <c r="F70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7038</v>
+        <v>0.6841</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Ket_Qua_Xep_Lich.xlsx
+++ b/outputs/Ket_Qua_Xep_Lich.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CB014, CB038, CB011, CB072</t>
+          <t>CB014, CB038, CB011, CB042</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CB007, CB061, CB046, CB001</t>
+          <t>CB034, CB061, CB067, CB001</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CB071</t>
+          <t>CB063</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CB004, CB064, CB025, CB038, CB042, CB050, CB026, CB010, CB033, CB046, CB067, CB018, CB073, CB055, CB024, CB059, CB072, CB028, CB047, CB006, CB057, CB053, CB041, CB003, CB045, CB065, CB061, CB032, CB048, CB066, CB039, CB008</t>
+          <t>CB004, CB013, CB025, CB038, CB042, CB020, CB026, CB010, CB009, CB030, CB067, CB012, CB070, CB055, CB024, CB059, CB072, CB028, CB047, CB027, CB057, CB053, CB046, CB003, CB045, CB065, CB061, CB032, CB048, CB068, CB039, CB008</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CB012, CB037, CB069, CB031, CB071, CB015, CB062, CB005, CB063, CB030, CB011, CB054, CB049, CB060, CB019, CB035, CB016, CB001, CB072, CB007, CB022, CB051, CB052, CB042, CB017, CB013, CB065, CB066</t>
+          <t>CB012, CB037, CB069, CB032, CB071, CB015, CB062, CB005, CB063, CB030, CB011, CB014, CB049, CB060, CB019, CB035, CB016, CB001, CB073, CB007, CB022, CB051, CB052, CB041, CB017, CB013, CB006, CB066</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CB020</t>
+          <t>CB036</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CB068</t>
+          <t>CB054</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CB007, CB018</t>
+          <t>CB055, CB014</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CB030, CB058, CB039, CB048, CB041, CB033, CB057, CB001, CB038, CB025, CB061, CB029, CB008, CB034, CB002, CB054, CB036, CB069, CB064, CB053, CB015, CB022, CB012, CB005, CB070, CB059, CB023, CB016, CB045, CB035</t>
+          <t>CB030, CB058, CB039, CB048, CB041, CB047, CB057, CB001, CB038, CB025, CB061, CB029, CB043, CB056, CB002, CB054, CB036, CB069, CB064, CB053, CB015, CB040, CB012, CB005, CB070, CB059, CB023, CB031, CB045, CB035</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CB060, CB011, CB065</t>
+          <t>CB062, CB011, CB065</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CB032, CB006, CB055, CB033, CB063, CB035, CB019, CB052, CB028, CB009, CB031, CB010, CB067, CB042, CB014, CB073, CB016, CB026, CB027, CB002, CB013, CB037, CB051, CB072, CB021, CB058, CB056, CB001, CB017, CB043</t>
+          <t>CB032, CB006, CB055, CB033, CB063, CB050, CB019, CB071, CB028, CB009, CB031, CB010, CB067, CB042, CB018, CB073, CB016, CB026, CB027, CB002, CB013, CB072, CB051, CB066, CB021, CB058, CB007, CB001, CB017, CB043</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CB044, CB003, CB024</t>
+          <t>CB044, CB037, CB022</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CB060, CB065, CB049</t>
+          <t>CB065, CB008, CB049</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CB049, CB063</t>
+          <t>CB053, CB055</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CB041, CB061, CB018, CB056, CB067, CB058, CB040, CB065, CB035, CB026, CB052, CB050, CB057, CB043, CB055, CB032, CB006</t>
+          <t>CB022, CB061, CB018, CB056, CB067, CB058, CB003, CB063, CB031, CB026, CB062, CB050, CB057, CB043, CB055, CB032, CB068</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CB019, CB008, CB022, CB029, CB063, CB069, CB002, CB026, CB060, CB065, CB020, CB007, CB024, CB073, CB067, CB010, CB032, CB054, CB051, CB023, CB050, CB056, CB034, CB055, CB040, CB066, CB031, CB059, CB003, CB043, CB018, CB004</t>
+          <t>CB014, CB008, CB022, CB029, CB063, CB069, CB002, CB058, CB060, CB065, CB020, CB007, CB024, CB005, CB067, CB010, CB025, CB054, CB051, CB023, CB050, CB056, CB034, CB055, CB036, CB066, CB031, CB071, CB003, CB043, CB018, CB004</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CB004, CB012, CB014, CB053, CB070, CB015, CB011, CB048, CB028, CB057, CB071, CB046, CB030, CB033, CB047, CB016, CB036, CB072, CB041, CB034, CB020, CB025, CB051, CB010, CB061, CB027, CB005, CB021, CB017, CB035, CB042, CB068</t>
+          <t>CB002, CB003, CB014, CB053, CB070, CB015, CB011, CB019, CB028, CB057, CB039, CB044, CB030, CB006, CB052, CB016, CB036, CB072, CB041, CB034, CB013, CB025, CB048, CB033, CB061, CB027, CB007, CB021, CB017, CB009, CB042, CB068</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CB029, CB003, CB009, CB052, CB023, CB026, CB054, CB058, CB060, CB013, CB032, CB012, CB044, CB067, CB066</t>
+          <t>CB029, CB064, CB024, CB004, CB023, CB026, CB072, CB018, CB060, CB047, CB010, CB012, CB035, CB067, CB066</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CB036, CB037</t>
+          <t>CB049, CB037</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CB002, CB025, CB016, CB062, CB032</t>
+          <t>CB024, CB035, CB016, CB062, CB032</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CB006, CB050, CB052, CB037, CB028, CB070, CB009, CB056, CB013, CB071, CB059, CB029, CB066, CB060, CB047, CB023, CB027, CB012, CB042, CB040</t>
+          <t>CB006, CB064, CB065, CB037, CB028, CB021, CB020, CB056, CB013, CB068, CB059, CB029, CB066, CB061, CB047, CB023, CB048, CB012, CB034, CB040</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CB031, CB003, CB019, CB017, CB072, CB045, CB063, CB014, CB055, CB007, CB068, CB054, CB058, CB036, CB035</t>
+          <t>CB031, CB003, CB019, CB017, CB072, CB045, CB063, CB014, CB055, CB007, CB069, CB053, CB058, CB036, CB050</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CB057</t>
+          <t>CB052</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CB020, CB051</t>
+          <t>CB020, CB029</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CB051, CB067, CB070, CB047, CB009, CB008, CB026, CB043, CB018, CB058, CB052, CB040, CB071, CB033, CB053, CB007, CB066, CB056, CB039, CB068, CB064, CB055, CB035, CB050, CB059, CB060, CB038, CB045, CB005, CB046, CB014</t>
+          <t>CB051, CB067, CB070, CB047, CB009, CB003, CB026, CB045, CB032, CB058, CB002, CB040, CB071, CB033, CB053, CB007, CB066, CB056, CB054, CB068, CB064, CB055, CB069, CB050, CB059, CB060, CB038, CB019, CB005, CB046, CB043</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CB041, CB034, CB059, CB062, CB049, CB013, CB024, CB067, CB031, CB015, CB050, CB048, CB042, CB025, CB017, CB044, CB023, CB054, CB065, CB069, CB057, CB022, CB032, CB063, CB073, CB006, CB011, CB030, CB029, CB072, CB002</t>
+          <t>CB041, CB034, CB059, CB062, CB049, CB013, CB024, CB067, CB039, CB015, CB050, CB048, CB042, CB025, CB017, CB044, CB023, CB052, CB065, CB069, CB057, CB037, CB035, CB063, CB073, CB006, CB061, CB030, CB029, CB072, CB004</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CB066, CB047, CB068, CB018, CB052, CB061, CB004, CB057, CB008, CB014, CB016, CB060, CB053, CB026, CB035, CB051, CB070, CB049, CB003, CB010, CB013, CB020, CB036, CB042, CB028, CB058, CB022, CB031, CB019, CB040, CB038</t>
+          <t>CB066, CB047, CB068, CB018, CB052, CB073, CB029, CB064, CB008, CB014, CB016, CB060, CB053, CB026, CB035, CB048, CB070, CB049, CB003, CB010, CB013, CB020, CB036, CB042, CB034, CB058, CB022, CB031, CB019, CB040, CB038</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CB004, CB041, CB011, CB017, CB015, CB025, CB045, CB067, CB021, CB027, CB005, CB002, CB071, CB055, CB037, CB029, CB054, CB039, CB001, CB009, CB024</t>
+          <t>CB004, CB041, CB011, CB012, CB050, CB015, CB023, CB067, CB032, CB027, CB005, CB057, CB071, CB052, CB037, CB026, CB060, CB039, CB001, CB054, CB028</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CB071</t>
+          <t>CB041</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CB055</t>
+          <t>CB027</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CB036, CB072, CB001, CB040, CB039</t>
+          <t>CB036, CB072, CB001, CB040, CB015</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CB058, CB021, CB037, CB011, CB026, CB063, CB048, CB045, CB033, CB007, CB065, CB008, CB051, CB006, CB046, CB028, CB056, CB053, CB003, CB070, CB064, CB029, CB044, CB020, CB018, CB014, CB034, CB059, CB054, CB062</t>
+          <t>CB058, CB021, CB037, CB011, CB026, CB063, CB048, CB045, CB033, CB007, CB065, CB008, CB051, CB006, CB046, CB028, CB056, CB053, CB003, CB070, CB066, CB029, CB044, CB020, CB018, CB014, CB034, CB059, CB031, CB062</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CB017</t>
+          <t>CB019</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CB037, CB047</t>
+          <t>CB036, CB060</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CB049</t>
+          <t>CB047</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CB002, CB009, CB021, CB042, CB032, CB043, CB069, CB020, CB047, CB006</t>
+          <t>CB002, CB007, CB064, CB037, CB026, CB061, CB060, CB020, CB047, CB003</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CB019, CB038, CB035, CB059</t>
+          <t>CB021, CB008, CB035, CB059</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CB021, CB059, CB027, CB009, CB001, CB065, CB030, CB072, CB064, CB032, CB063, CB005, CB015, CB051, CB026, CB041, CB073, CB043, CB022, CB004, CB025, CB018, CB060, CB050, CB056, CB008, CB062, CB068, CB039</t>
+          <t>CB042, CB054, CB027, CB009, CB001, CB065, CB030, CB072, CB047, CB028, CB021, CB005, CB015, CB051, CB070, CB045, CB073, CB043, CB022, CB004, CB025, CB018, CB060, CB049, CB056, CB008, CB062, CB068, CB039</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CB073, CB009</t>
+          <t>CB035, CB009</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CB021</t>
+          <t>CB012</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CB056</t>
+          <t>CB051</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CB061</t>
+          <t>CB004</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CB068, CB062, CB036, CB002, CB070, CB049, CB016, CB030, CB021, CB001, CB069, CB050, CB032, CB044</t>
+          <t>CB068, CB005, CB037, CB027, CB045, CB054, CB071, CB066, CB021, CB001, CB017, CB050, CB032, CB040</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CB007</t>
+          <t>CB009</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CB011, CB022, CB073</t>
+          <t>CB020, CB022, CB073</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CB072, CB070, CB031, CB030, CB049, CB015, CB048, CB012, CB016, CB028, CB039, CB046, CB002, CB073, CB043, CB053, CB065, CB036, CB037, CB051, CB056, CB019</t>
+          <t>CB072, CB025, CB006, CB002, CB049, CB015, CB048, CB012, CB016, CB028, CB039, CB046, CB059, CB073, CB054, CB053, CB065, CB010, CB037, CB051, CB056, CB013</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CB040, CB024, CB025, CB003, CB057, CB050, CB058, CB035, CB007, CB018, CB014, CB017, CB004, CB041, CB063, CB028, CB044, CB071, CB066, CB005, CB070, CB023, CB047, CB020, CB054, CB061, CB019, CB068, CB001, CB062</t>
+          <t>CB040, CB024, CB021, CB003, CB057, CB050, CB058, CB035, CB007, CB018, CB038, CB017, CB004, CB041, CB063, CB028, CB044, CB071, CB046, CB005, CB070, CB033, CB047, CB020, CB042, CB061, CB019, CB068, CB001, CB067</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CB037, CB049, CB029, CB073, CB036</t>
+          <t>CB023, CB044, CB029, CB073, CB036</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CB005, CB051, CB038, CB036, CB017, CB071, CB018, CB037, CB054, CB056, CB013, CB006, CB068, CB024, CB030, CB049, CB043, CB011, CB064, CB060, CB053, CB055, CB048, CB062, CB026, CB045, CB039, CB021, CB040, CB020, CB008, CB041</t>
+          <t>CB005, CB051, CB038, CB027, CB010, CB071, CB018, CB037, CB054, CB056, CB004, CB006, CB070, CB017, CB030, CB049, CB043, CB011, CB064, CB033, CB057, CB055, CB048, CB062, CB026, CB052, CB002, CB021, CB040, CB020, CB008, CB041</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CB012, CB040, CB044, CB058, CB015, CB065</t>
+          <t>CB006, CB040, CB044, CB058, CB072, CB073</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CB001, CB035, CB059, CB027, CB053, CB021, CB055, CB061, CB017, CB038, CB028, CB049, CB005, CB069, CB031, CB011, CB033, CB014, CB003, CB009, CB057, CB046, CB037, CB063, CB006, CB019, CB023, CB030, CB066, CB026, CB064</t>
+          <t>CB001, CB035, CB059, CB027, CB007, CB022, CB055, CB051, CB017, CB038, CB028, CB049, CB065, CB069, CB039, CB011, CB033, CB014, CB061, CB009, CB057, CB046, CB030, CB063, CB016, CB019, CB023, CB029, CB066, CB026, CB064</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CB004, CB025</t>
+          <t>CB010, CB025</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CB044, CB042, CB048, CB073, CB071, CB052, CB012, CB009, CB037, CB054, CB034, CB067, CB020, CB046, CB036, CB008, CB024, CB029, CB015, CB039, CB032</t>
+          <t>CB044, CB042, CB068, CB073, CB071, CB052, CB005, CB009, CB037, CB054, CB034, CB067, CB020, CB046, CB036, CB008, CB024, CB029, CB015, CB043, CB032</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CB010</t>
+          <t>CB013</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CB070, CB013</t>
+          <t>CB070, CB012</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CB047, CB027, CB051, CB045, CB011, CB043, CB003, CB010, CB013, CB022, CB038, CB053, CB016, CB024, CB049, CB004, CB069, CB012, CB059, CB046, CB055, CB064, CB063, CB018, CB015, CB061, CB067, CB026, CB062, CB060, CB044</t>
+          <t>CB047, CB027, CB051, CB045, CB011, CB043, CB036, CB010, CB071, CB022, CB038, CB053, CB016, CB024, CB049, CB017, CB069, CB012, CB059, CB046, CB055, CB064, CB063, CB018, CB015, CB033, CB021, CB026, CB062, CB060, CB044</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CB023</t>
+          <t>CB025</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CB054, CB009, CB005</t>
+          <t>CB056, CB009, CB005</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CB025, CB015, CB039, CB052, CB033, CB010</t>
+          <t>CB025, CB015, CB039, CB052, CB045, CB014</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CB041, CB069, CB034, CB038</t>
+          <t>CB041, CB069, CB024, CB038</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CB045, CB014, CB028, CB029</t>
+          <t>CB041, CB011, CB018, CB054</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CB002, CB007, CB010, CB044, CB048, CB027</t>
+          <t>CB002, CB007, CB010, CB044, CB060, CB046</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CB033, CB004, CB022, CB027, CB073, CB024</t>
+          <t>CB033, CB031, CB030, CB039, CB073, CB024</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CB034, CB023, CB064, CB045</t>
+          <t>CB016, CB023, CB032, CB045</t>
         </is>
       </c>
     </row>
@@ -3850,11 +3850,11 @@
         <v>21.4</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3908,11 +3908,11 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3937,11 +3937,11 @@
         <v>7.9</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3995,11 +3995,11 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4053,11 +4053,11 @@
         <v>2.1</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4082,11 +4082,11 @@
         <v>18.9</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4111,11 +4111,11 @@
         <v>24.4</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
         <v>10.8</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4372,11 +4372,11 @@
         <v>14.3</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4575,11 +4575,11 @@
         <v>10.6</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4633,11 +4633,11 @@
         <v>6.9</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4720,11 +4720,11 @@
         <v>11.7</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4807,11 +4807,11 @@
         <v>12.1</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5155,11 +5155,11 @@
         <v>23.3</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5213,11 +5213,11 @@
         <v>23.7</v>
       </c>
       <c r="F50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5271,11 +5271,11 @@
         <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5358,11 +5358,11 @@
         <v>16</v>
       </c>
       <c r="F55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5503,11 +5503,11 @@
         <v>24.8</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5677,11 +5677,11 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5706,11 +5706,11 @@
         <v>6.7</v>
       </c>
       <c r="F67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5735,11 +5735,11 @@
         <v>9.5</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5764,11 +5764,11 @@
         <v>10.8</v>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6841</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Ket_Qua_Xep_Lich.xlsx
+++ b/outputs/Ket_Qua_Xep_Lich.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CB014, CB038, CB011, CB042</t>
+          <t>CB030, CB004, CB025, CB056</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CB034, CB061, CB067, CB001</t>
+          <t>CB021, CB006, CB017, CB004</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CB063</t>
+          <t>CB039</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CB004, CB013, CB025, CB038, CB042, CB020, CB026, CB010, CB009, CB030, CB067, CB012, CB070, CB055, CB024, CB059, CB072, CB028, CB047, CB027, CB057, CB053, CB046, CB003, CB045, CB065, CB061, CB032, CB048, CB068, CB039, CB008</t>
+          <t>CB046, CB031, CB005, CB058, CB002, CB055, CB039, CB029, CB038, CB040, CB016, CB003, CB020, CB007, CB072, CB013, CB048, CB012, CB024, CB061, CB071, CB052, CB056, CB022, CB030, CB064, CB044, CB019, CB025, CB042, CB035, CB027</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CB012, CB037, CB069, CB032, CB071, CB015, CB062, CB005, CB063, CB030, CB011, CB014, CB049, CB060, CB019, CB035, CB016, CB001, CB073, CB007, CB022, CB051, CB052, CB041, CB017, CB013, CB006, CB066</t>
+          <t>CB067, CB014, CB033, CB070, CB060, CB008, CB045, CB050, CB062, CB073, CB010, CB001, CB057, CB058, CB023, CB037, CB064, CB006, CB066, CB017, CB061, CB032, CB018, CB009, CB065, CB020, CB069, CB026</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CB036</t>
+          <t>CB019</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CB054</t>
+          <t>CB015</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CB055, CB014</t>
+          <t>CB037, CB041</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CB030, CB058, CB039, CB048, CB041, CB047, CB057, CB001, CB038, CB025, CB061, CB029, CB043, CB056, CB002, CB054, CB036, CB069, CB064, CB053, CB015, CB040, CB012, CB005, CB070, CB059, CB023, CB031, CB045, CB035</t>
+          <t>CB019, CB028, CB014, CB009, CB027, CB060, CB015, CB032, CB029, CB030, CB048, CB063, CB045, CB068, CB016, CB034, CB005, CB071, CB022, CB064, CB038, CB011, CB007, CB024, CB066, CB069, CB053, CB036, CB059, CB010</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CB062, CB011, CB065</t>
+          <t>CB013, CB002, CB043</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CB032, CB006, CB055, CB033, CB063, CB050, CB019, CB071, CB028, CB009, CB031, CB010, CB067, CB042, CB018, CB073, CB016, CB026, CB027, CB002, CB013, CB072, CB051, CB066, CB021, CB058, CB007, CB001, CB017, CB043</t>
+          <t>CB040, CB031, CB073, CB038, CB052, CB014, CB070, CB065, CB061, CB054, CB026, CB034, CB028, CB056, CB049, CB019, CB072, CB071, CB017, CB007, CB047, CB069, CB037, CB033, CB055, CB059, CB021, CB020, CB008, CB041</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CB044, CB037, CB022</t>
+          <t>CB006, CB023, CB018</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CB020, CB034, CB029, CB068</t>
+          <t>CB044, CB068, CB042, CB013</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CB065, CB008, CB049</t>
+          <t>CB053, CB062, CB018</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CB053, CB055</t>
+          <t>CB008, CB062</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CB022, CB061, CB018, CB056, CB067, CB058, CB003, CB063, CB031, CB026, CB062, CB050, CB057, CB043, CB055, CB032, CB068</t>
+          <t>CB014, CB050, CB034, CB051, CB068, CB010, CB065, CB037, CB053, CB001, CB060, CB038, CB062, CB040, CB009, CB049, CB057</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CB046, CB033, CB066</t>
+          <t>CB001, CB036, CB003</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CB013</t>
+          <t>CB041</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CB014, CB008, CB022, CB029, CB063, CB069, CB002, CB058, CB060, CB065, CB020, CB007, CB024, CB005, CB067, CB010, CB025, CB054, CB051, CB023, CB050, CB056, CB034, CB055, CB036, CB066, CB031, CB071, CB003, CB043, CB018, CB004</t>
+          <t>CB072, CB046, CB026, CB045, CB003, CB035, CB014, CB061, CB057, CB027, CB011, CB053, CB062, CB032, CB054, CB069, CB070, CB063, CB066, CB025, CB022, CB042, CB052, CB039, CB055, CB050, CB056, CB016, CB021, CB017, CB030, CB044</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CB002, CB003, CB014, CB053, CB070, CB015, CB011, CB019, CB028, CB057, CB039, CB044, CB030, CB006, CB052, CB016, CB036, CB072, CB041, CB034, CB013, CB025, CB048, CB033, CB061, CB027, CB007, CB021, CB017, CB009, CB042, CB068</t>
+          <t>CB013, CB036, CB051, CB071, CB059, CB048, CB012, CB052, CB042, CB018, CB065, CB003, CB037, CB060, CB010, CB008, CB015, CB006, CB028, CB033, CB043, CB029, CB073, CB024, CB022, CB005, CB009, CB050, CB016, CB040, CB004, CB053</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CB029, CB064, CB024, CB004, CB023, CB026, CB072, CB018, CB060, CB047, CB010, CB012, CB035, CB067, CB066</t>
+          <t>CB015, CB010, CB002, CB033, CB058, CB023, CB039, CB027, CB007, CB020, CB001, CB026, CB035, CB032, CB034</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CB049, CB037</t>
+          <t>CB021, CB019</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CB024, CB035, CB016, CB062, CB032</t>
+          <t>CB017, CB072, CB042, CB055, CB051</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CB006, CB064, CB065, CB037, CB028, CB021, CB020, CB056, CB013, CB068, CB059, CB029, CB066, CB061, CB047, CB023, CB048, CB012, CB034, CB040</t>
+          <t>CB020, CB058, CB057, CB026, CB035, CB031, CB036, CB033, CB030, CB006, CB013, CB045, CB065, CB005, CB070, CB024, CB018, CB047, CB063, CB001</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CB031, CB003, CB019, CB017, CB072, CB045, CB063, CB014, CB055, CB007, CB069, CB053, CB058, CB036, CB050</t>
+          <t>CB020, CB043, CB063, CB001, CB071, CB046, CB012, CB040, CB047, CB050, CB066, CB034, CB064, CB019, CB038</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CB052</t>
+          <t>CB059</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CB004, CB023, CB012</t>
+          <t>CB022, CB037, CB065</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CB020, CB029</t>
+          <t>CB040, CB012</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CB051, CB067, CB070, CB047, CB009, CB003, CB026, CB045, CB032, CB058, CB002, CB040, CB071, CB033, CB053, CB007, CB066, CB056, CB054, CB068, CB064, CB055, CB069, CB050, CB059, CB060, CB038, CB019, CB005, CB046, CB043</t>
+          <t>CB066, CB020, CB010, CB050, CB003, CB033, CB030, CB051, CB064, CB041, CB021, CB008, CB037, CB036, CB002, CB073, CB026, CB015, CB018, CB072, CB067, CB043, CB068, CB022, CB053, CB062, CB056, CB029, CB065, CB011, CB060</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CB041, CB034, CB059, CB062, CB049, CB013, CB024, CB067, CB039, CB015, CB050, CB048, CB042, CB025, CB017, CB044, CB023, CB052, CB065, CB069, CB057, CB037, CB035, CB063, CB073, CB006, CB061, CB030, CB029, CB072, CB004</t>
+          <t>CB023, CB051, CB009, CB031, CB063, CB014, CB044, CB018, CB071, CB019, CB053, CB058, CB061, CB024, CB070, CB048, CB064, CB052, CB072, CB045, CB038, CB057, CB059, CB021, CB025, CB035, CB067, CB016, CB017, CB013, CB032</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CB066, CB047, CB068, CB018, CB052, CB073, CB029, CB064, CB008, CB014, CB016, CB060, CB053, CB026, CB035, CB048, CB070, CB049, CB003, CB010, CB013, CB020, CB036, CB042, CB034, CB058, CB022, CB031, CB019, CB040, CB038</t>
+          <t>CB006, CB068, CB040, CB008, CB060, CB053, CB005, CB070, CB015, CB035, CB072, CB025, CB004, CB013, CB011, CB047, CB045, CB031, CB007, CB049, CB010, CB009, CB058, CB063, CB001, CB044, CB002, CB057, CB026, CB066, CB073</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CB004, CB041, CB011, CB012, CB050, CB015, CB023, CB067, CB032, CB027, CB005, CB057, CB071, CB052, CB037, CB026, CB060, CB039, CB001, CB054, CB028</t>
+          <t>CB008, CB030, CB034, CB054, CB005, CB028, CB007, CB042, CB032, CB019, CB004, CB017, CB018, CB055, CB031, CB061, CB069, CB068, CB027, CB043, CB036</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CB041</t>
+          <t>CB063</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CB027</t>
+          <t>CB044</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CB012</t>
+          <t>CB003</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CB036, CB072, CB001, CB040, CB015</t>
+          <t>CB054, CB032, CB046, CB070, CB003</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CB058, CB021, CB037, CB011, CB026, CB063, CB048, CB045, CB033, CB007, CB065, CB008, CB051, CB006, CB046, CB028, CB056, CB053, CB003, CB070, CB066, CB029, CB044, CB020, CB018, CB014, CB034, CB059, CB031, CB062</t>
+          <t>CB001, CB041, CB052, CB065, CB069, CB009, CB012, CB023, CB060, CB061, CB056, CB042, CB004, CB002, CB025, CB015, CB007, CB024, CB045, CB067, CB030, CB071, CB026, CB033, CB016, CB038, CB059, CB055, CB050, CB064</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CB019</t>
+          <t>CB035</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CB036, CB060</t>
+          <t>CB042, CB020</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CB047</t>
+          <t>CB025</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CB034, CB066, CB068, CB023</t>
+          <t>CB058, CB030, CB016, CB042</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CB002, CB007, CB064, CB037, CB026, CB061, CB060, CB020, CB047, CB003</t>
+          <t>CB067, CB014, CB015, CB024, CB053, CB039, CB029, CB059, CB063, CB002</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CB016, CB031, CB027, CB070, CB071, CB010, CB063</t>
+          <t>CB058, CB070, CB011, CB056, CB066, CB073, CB020</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CB021, CB008, CB035, CB059</t>
+          <t>CB016, CB044, CB061, CB054</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CB030, CB036</t>
+          <t>CB045, CB048</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CB003, CB052</t>
+          <t>CB019, CB043</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CB042, CB054, CB027, CB009, CB001, CB065, CB030, CB072, CB047, CB028, CB021, CB005, CB015, CB051, CB070, CB045, CB073, CB043, CB022, CB004, CB025, CB018, CB060, CB049, CB056, CB008, CB062, CB068, CB039</t>
+          <t>CB035, CB049, CB046, CB059, CB023, CB061, CB054, CB015, CB071, CB069, CB018, CB005, CB027, CB058, CB017, CB073, CB028, CB072, CB022, CB008, CB011, CB048, CB002, CB012, CB031, CB057, CB047, CB055, CB041</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CB055</t>
+          <t>CB041</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CB035, CB009</t>
+          <t>CB046, CB044</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CB012</t>
+          <t>CB050</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CB051</t>
+          <t>CB033</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CB004</t>
+          <t>CB039</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CB068, CB005, CB037, CB027, CB045, CB054, CB071, CB066, CB021, CB001, CB017, CB050, CB032, CB040</t>
+          <t>CB021, CB036, CB048, CB008, CB049, CB023, CB052, CB068, CB022, CB028, CB006, CB027, CB038, CB043</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CB009</t>
+          <t>CB047</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CB020, CB022, CB073</t>
+          <t>CB041, CB046, CB051</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CB072, CB025, CB006, CB002, CB049, CB015, CB048, CB012, CB016, CB028, CB039, CB046, CB059, CB073, CB054, CB053, CB065, CB010, CB037, CB051, CB056, CB013</t>
+          <t>CB003, CB001, CB029, CB058, CB030, CB043, CB027, CB016, CB039, CB026, CB038, CB067, CB072, CB060, CB054, CB053, CB044, CB034, CB010, CB037, CB049, CB045</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CB040, CB024, CB021, CB003, CB057, CB050, CB058, CB035, CB007, CB018, CB038, CB017, CB004, CB041, CB063, CB028, CB044, CB071, CB046, CB005, CB070, CB033, CB047, CB020, CB042, CB061, CB019, CB068, CB001, CB067</t>
+          <t>CB050, CB073, CB041, CB028, CB044, CB052, CB023, CB051, CB013, CB056, CB071, CB005, CB068, CB033, CB012, CB064, CB060, CB014, CB031, CB063, CB022, CB070, CB017, CB004, CB003, CB048, CB066, CB024, CB069, CB062</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CB023, CB044, CB029, CB073, CB036</t>
+          <t>CB040, CB057, CB011, CB049, CB058</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CB005, CB051, CB038, CB027, CB010, CB071, CB018, CB037, CB054, CB056, CB004, CB006, CB070, CB017, CB030, CB049, CB043, CB011, CB064, CB033, CB057, CB055, CB048, CB062, CB026, CB052, CB002, CB021, CB040, CB020, CB008, CB041</t>
+          <t>CB013, CB020, CB055, CB007, CB050, CB022, CB030, CB039, CB046, CB016, CB071, CB064, CB072, CB031, CB026, CB040, CB066, CB025, CB034, CB037, CB005, CB015, CB038, CB068, CB035, CB017, CB047, CB010, CB049, CB023, CB070, CB059</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CB006, CB040, CB044, CB058, CB072, CB073</t>
+          <t>CB047, CB009, CB062, CB045, CB049, CB073</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CB001, CB035, CB059, CB027, CB007, CB022, CB055, CB051, CB017, CB038, CB028, CB049, CB065, CB069, CB039, CB011, CB033, CB014, CB061, CB009, CB057, CB046, CB030, CB063, CB016, CB019, CB023, CB029, CB066, CB026, CB064</t>
+          <t>CB014, CB001, CB065, CB008, CB022, CB011, CB041, CB055, CB009, CB036, CB054, CB067, CB052, CB007, CB051, CB004, CB061, CB047, CB006, CB025, CB019, CB035, CB056, CB046, CB039, CB013, CB027, CB023, CB043, CB010, CB034</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CB010, CB025</t>
+          <t>CB002, CB069</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CB044, CB042, CB068, CB073, CB071, CB052, CB005, CB009, CB037, CB054, CB034, CB067, CB020, CB046, CB036, CB008, CB024, CB029, CB015, CB043, CB032</t>
+          <t>CB062, CB034, CB031, CB025, CB042, CB027, CB004, CB066, CB036, CB024, CB065, CB029, CB032, CB028, CB057, CB033, CB005, CB040, CB067, CB021, CB009</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CB013</t>
+          <t>CB038</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CB070, CB012</t>
+          <t>CB055, CB006</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CB052</t>
+          <t>CB069</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CB047, CB027, CB051, CB045, CB011, CB043, CB036, CB010, CB071, CB022, CB038, CB053, CB016, CB024, CB049, CB017, CB069, CB012, CB059, CB046, CB055, CB064, CB063, CB018, CB015, CB033, CB021, CB026, CB062, CB060, CB044</t>
+          <t>CB027, CB023, CB054, CB048, CB007, CB067, CB006, CB028, CB037, CB004, CB011, CB047, CB053, CB057, CB032, CB059, CB049, CB046, CB033, CB044, CB056, CB036, CB024, CB002, CB029, CB012, CB051, CB001, CB005, CB003, CB039</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CB025</t>
+          <t>CB018</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CB005</t>
+          <t>CB025</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CB056, CB009, CB005</t>
+          <t>CB055, CB008, CB073</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CB031, CB057, CB040, CB047</t>
+          <t>CB041, CB065, CB059, CB047</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CB050, CB043</t>
+          <t>CB012, CB016</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CB025, CB015, CB039, CB052, CB045, CB014</t>
+          <t>CB067, CB006, CB029, CB064, CB032, CB049</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CB041, CB069, CB024, CB038</t>
+          <t>CB007, CB034, CB040, CB014</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CB064, CB062, CB042, CB006, CB019, CB022</t>
+          <t>CB013, CB003, CB063, CB042, CB037, CB043</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CB041, CB011, CB018, CB054</t>
+          <t>CB021, CB068, CB029, CB062</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CB002, CB007, CB010, CB044, CB060, CB046</t>
+          <t>CB048, CB043, CB018, CB054, CB052, CB060</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CB033, CB031, CB030, CB039, CB073, CB024</t>
+          <t>CB021, CB032, CB012, CB002, CB036, CB046</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CB016, CB023, CB032, CB045</t>
+          <t>CB015, CB050, CB028, CB009</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CB069, CB048, CB008, CB002</t>
+          <t>CB011, CB064, CB051, CB047</t>
         </is>
       </c>
     </row>
@@ -3821,11 +3821,11 @@
         <v>4.4</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3850,11 +3850,11 @@
         <v>21.4</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3937,11 +3937,11 @@
         <v>7.9</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
         <v>3.8</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4024,11 +4024,11 @@
         <v>5.3</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4053,11 +4053,11 @@
         <v>2.1</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4082,11 +4082,11 @@
         <v>18.9</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
         <v>10.8</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4169,11 +4169,11 @@
         <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4256,11 +4256,11 @@
         <v>16.6</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4372,11 +4372,11 @@
         <v>14.3</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4430,11 +4430,11 @@
         <v>13.9</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4517,11 +4517,11 @@
         <v>5.8</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4546,11 +4546,11 @@
         <v>22.3</v>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4633,11 +4633,11 @@
         <v>6.9</v>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4662,11 +4662,11 @@
         <v>5.7</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4720,11 +4720,11 @@
         <v>11.7</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4749,11 +4749,11 @@
         <v>22.6</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4778,11 +4778,11 @@
         <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4836,11 +4836,11 @@
         <v>5.8</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4894,11 +4894,11 @@
         <v>5.4</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4952,11 +4952,11 @@
         <v>5.5</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4981,11 +4981,11 @@
         <v>5.1</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5010,11 +5010,11 @@
         <v>19.8</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5039,11 +5039,11 @@
         <v>23.5</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5068,11 +5068,11 @@
         <v>23.4</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5126,11 +5126,11 @@
         <v>2.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5213,11 +5213,11 @@
         <v>23.7</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
         <v>14.7</v>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5271,11 +5271,11 @@
         <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5300,11 +5300,11 @@
         <v>24.7</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5329,11 +5329,11 @@
         <v>5.4</v>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5358,11 +5358,11 @@
         <v>16</v>
       </c>
       <c r="F55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5387,11 +5387,11 @@
         <v>5.7</v>
       </c>
       <c r="F56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
+          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5474,11 +5474,11 @@
         <v>7.5</v>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5503,11 +5503,11 @@
         <v>24.8</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5532,11 +5532,11 @@
         <v>10.3</v>
       </c>
       <c r="F61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5619,11 +5619,11 @@
         <v>23.3</v>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5648,11 +5648,11 @@
         <v>16.5</v>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5677,11 +5677,11 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5706,11 +5706,11 @@
         <v>6.7</v>
       </c>
       <c r="F67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5735,11 +5735,11 @@
         <v>9.5</v>
       </c>
       <c r="F68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5764,11 +5764,11 @@
         <v>10.8</v>
       </c>
       <c r="F69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5822,11 +5822,11 @@
         <v>18.2</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5851,11 +5851,11 @@
         <v>6.2</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5909,11 +5909,11 @@
         <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.76</v>
+        <v>0.5256</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Ket_Qua_Xep_Lich.xlsx
+++ b/outputs/Ket_Qua_Xep_Lich.xlsx
@@ -502,11 +502,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CB030, CB004, CB025, CB056</t>
+          <t>CB058, CB001</t>
         </is>
       </c>
     </row>
@@ -543,11 +543,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CB021, CB006, CB017, CB004</t>
+          <t>CB005</t>
         </is>
       </c>
     </row>
@@ -584,11 +584,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CB039</t>
+          <t>CB001, CB027, CB047, CB007, CB019, CB015</t>
         </is>
       </c>
     </row>
@@ -625,11 +625,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CB046, CB031, CB005, CB058, CB002, CB055, CB039, CB029, CB038, CB040, CB016, CB003, CB020, CB007, CB072, CB013, CB048, CB012, CB024, CB061, CB071, CB052, CB056, CB022, CB030, CB064, CB044, CB019, CB025, CB042, CB035, CB027</t>
+          <t>CB018, CB055, CB040, CB045, CB049, CB052</t>
         </is>
       </c>
     </row>
@@ -666,11 +666,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CB067, CB014, CB033, CB070, CB060, CB008, CB045, CB050, CB062, CB073, CB010, CB001, CB057, CB058, CB023, CB037, CB064, CB006, CB066, CB017, CB061, CB032, CB018, CB009, CB065, CB020, CB069, CB026</t>
+          <t>CB041, CB021, CB013, CB044, CB036</t>
         </is>
       </c>
     </row>
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CB019</t>
+          <t>CB028, CB056, CB029, CB009, CB070, CB058, CB016</t>
         </is>
       </c>
     </row>
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CB015</t>
+          <t>CB061, CB054, CB053, CB026, CB063, CB030, CB069, CB038, CB005</t>
         </is>
       </c>
     </row>
@@ -789,11 +789,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CB037, CB041</t>
+          <t>CB011, CB050, CB067, CB055, CB053, CB044, CB028, CB012</t>
         </is>
       </c>
     </row>
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CB019, CB028, CB014, CB009, CB027, CB060, CB015, CB032, CB029, CB030, CB048, CB063, CB045, CB068, CB016, CB034, CB005, CB071, CB022, CB064, CB038, CB011, CB007, CB024, CB066, CB069, CB053, CB036, CB059, CB010</t>
+          <t>CB003, CB068, CB059</t>
         </is>
       </c>
     </row>
@@ -871,11 +871,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CB013, CB002, CB043</t>
+          <t>CB006, CB065</t>
         </is>
       </c>
     </row>
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CB040, CB031, CB073, CB038, CB052, CB014, CB070, CB065, CB061, CB054, CB026, CB034, CB028, CB056, CB049, CB019, CB072, CB071, CB017, CB007, CB047, CB069, CB037, CB033, CB055, CB059, CB021, CB020, CB008, CB041</t>
+          <t>CB056, CB043, CB071, CB073, CB055, CB030, CB018, CB009, CB037</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CB006, CB023, CB018</t>
+          <t>CB061, CB027, CB011</t>
         </is>
       </c>
     </row>
@@ -994,11 +994,11 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CB044, CB068, CB042, CB013</t>
+          <t>CB017, CB023, CB040, CB036, CB054, CB031</t>
         </is>
       </c>
     </row>
@@ -1035,11 +1035,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CB053, CB062, CB018</t>
+          <t>CB042, CB021, CB005, CB001, CB029, CB004, CB045, CB008, CB072</t>
         </is>
       </c>
     </row>
@@ -1076,11 +1076,11 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CB008, CB062</t>
+          <t>CB067, CB033, CB018, CB004, CB046</t>
         </is>
       </c>
     </row>
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CB014, CB050, CB034, CB051, CB068, CB010, CB065, CB037, CB053, CB001, CB060, CB038, CB062, CB040, CB009, CB049, CB057</t>
+          <t>CB004, CB072, CB066, CB028, CB056, CB002, CB068, CB024, CB053</t>
         </is>
       </c>
     </row>
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CB001, CB036, CB003</t>
+          <t>CB034, CB010, CB057, CB019, CB050, CB018</t>
         </is>
       </c>
     </row>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CB041</t>
+          <t>CB024, CB039, CB019, CB017, CB052, CB033, CB060</t>
         </is>
       </c>
     </row>
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CB072, CB046, CB026, CB045, CB003, CB035, CB014, CB061, CB057, CB027, CB011, CB053, CB062, CB032, CB054, CB069, CB070, CB063, CB066, CB025, CB022, CB042, CB052, CB039, CB055, CB050, CB056, CB016, CB021, CB017, CB030, CB044</t>
+          <t>CB038, CB032, CB016</t>
         </is>
       </c>
     </row>
@@ -1281,11 +1281,11 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CB013, CB036, CB051, CB071, CB059, CB048, CB012, CB052, CB042, CB018, CB065, CB003, CB037, CB060, CB010, CB008, CB015, CB006, CB028, CB033, CB043, CB029, CB073, CB024, CB022, CB005, CB009, CB050, CB016, CB040, CB004, CB053</t>
+          <t>CB006, CB037, CB010</t>
         </is>
       </c>
     </row>
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CB015, CB010, CB002, CB033, CB058, CB023, CB039, CB027, CB007, CB020, CB001, CB026, CB035, CB032, CB034</t>
+          <t>CB041, CB015, CB042, CB036, CB034, CB060, CB048</t>
         </is>
       </c>
     </row>
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CB021, CB019</t>
+          <t>CB064, CB054, CB043</t>
         </is>
       </c>
     </row>
@@ -1404,11 +1404,11 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CB017, CB072, CB042, CB055, CB051</t>
+          <t>CB004, CB050, CB009</t>
         </is>
       </c>
     </row>
@@ -1445,11 +1445,11 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CB020, CB058, CB057, CB026, CB035, CB031, CB036, CB033, CB030, CB006, CB013, CB045, CB065, CB005, CB070, CB024, CB018, CB047, CB063, CB001</t>
+          <t>CB012, CB040, CB029, CB015, CB057, CB061, CB006, CB064</t>
         </is>
       </c>
     </row>
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CB020, CB043, CB063, CB001, CB071, CB046, CB012, CB040, CB047, CB050, CB066, CB034, CB064, CB019, CB038</t>
+          <t>CB017, CB065, CB035, CB044</t>
         </is>
       </c>
     </row>
@@ -1527,11 +1527,11 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CB059</t>
+          <t>CB034, CB051, CB013, CB070, CB001</t>
         </is>
       </c>
     </row>
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CB022, CB037, CB065</t>
+          <t>CB003, CB060, CB063, CB009, CB010</t>
         </is>
       </c>
     </row>
@@ -1609,11 +1609,11 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CB040, CB012</t>
+          <t>CB033, CB055, CB002</t>
         </is>
       </c>
     </row>
@@ -1650,11 +1650,11 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CB066, CB020, CB010, CB050, CB003, CB033, CB030, CB051, CB064, CB041, CB021, CB008, CB037, CB036, CB002, CB073, CB026, CB015, CB018, CB072, CB067, CB043, CB068, CB022, CB053, CB062, CB056, CB029, CB065, CB011, CB060</t>
+          <t>CB032, CB050, CB037, CB045, CB046, CB017, CB057, CB020, CB054</t>
         </is>
       </c>
     </row>
@@ -1691,11 +1691,11 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CB023, CB051, CB009, CB031, CB063, CB014, CB044, CB018, CB071, CB019, CB053, CB058, CB061, CB024, CB070, CB048, CB064, CB052, CB072, CB045, CB038, CB057, CB059, CB021, CB025, CB035, CB067, CB016, CB017, CB013, CB032</t>
+          <t>CB042, CB012, CB068, CB009, CB051</t>
         </is>
       </c>
     </row>
@@ -1732,11 +1732,11 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CB006, CB068, CB040, CB008, CB060, CB053, CB005, CB070, CB015, CB035, CB072, CB025, CB004, CB013, CB011, CB047, CB045, CB031, CB007, CB049, CB010, CB009, CB058, CB063, CB001, CB044, CB002, CB057, CB026, CB066, CB073</t>
+          <t>CB016, CB038, CB025, CB043, CB059, CB048, CB046</t>
         </is>
       </c>
     </row>
@@ -1773,11 +1773,11 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CB008, CB030, CB034, CB054, CB005, CB028, CB007, CB042, CB032, CB019, CB004, CB017, CB018, CB055, CB031, CB061, CB069, CB068, CB027, CB043, CB036</t>
+          <t>CB003</t>
         </is>
       </c>
     </row>
@@ -1814,11 +1814,11 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CB063</t>
+          <t>CB043, CB066, CB038</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CB044</t>
+          <t>CB003, CB031, CB018, CB047, CB021, CB061</t>
         </is>
       </c>
     </row>
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CB003</t>
+          <t>CB008, CB005</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CB054, CB032, CB046, CB070, CB003</t>
+          <t>CB051, CB041, CB067, CB027, CB064</t>
         </is>
       </c>
     </row>
@@ -1978,11 +1978,11 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CB001, CB041, CB052, CB065, CB069, CB009, CB012, CB023, CB060, CB061, CB056, CB042, CB004, CB002, CB025, CB015, CB007, CB024, CB045, CB067, CB030, CB071, CB026, CB033, CB016, CB038, CB059, CB055, CB050, CB064</t>
+          <t>CB053</t>
         </is>
       </c>
     </row>
@@ -2019,11 +2019,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CB035</t>
+          <t>CB060, CB049</t>
         </is>
       </c>
     </row>
@@ -2060,11 +2060,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CB042, CB020</t>
+          <t>CB056, CB026, CB008, CB006</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CB025</t>
+          <t>CB030</t>
         </is>
       </c>
     </row>
@@ -2142,11 +2142,11 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CB058, CB030, CB016, CB042</t>
+          <t>CB034</t>
         </is>
       </c>
     </row>
@@ -2183,11 +2183,11 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CB067, CB014, CB015, CB024, CB053, CB039, CB029, CB059, CB063, CB002</t>
+          <t>CB035</t>
         </is>
       </c>
     </row>
@@ -2224,11 +2224,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CB058, CB070, CB011, CB056, CB066, CB073, CB020</t>
+          <t>CB027, CB052, CB058, CB069</t>
         </is>
       </c>
     </row>
@@ -2265,11 +2265,11 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CB016, CB044, CB061, CB054</t>
+          <t>CB012, CB070, CB047, CB041, CB022, CB023, CB062</t>
         </is>
       </c>
     </row>
@@ -2306,11 +2306,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CB045, CB048</t>
+          <t>CB032</t>
         </is>
       </c>
     </row>
@@ -2347,11 +2347,11 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CB019, CB043</t>
+          <t>CB052, CB036, CB062, CB071</t>
         </is>
       </c>
     </row>
@@ -2388,11 +2388,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CB035, CB049, CB046, CB059, CB023, CB061, CB054, CB015, CB071, CB069, CB018, CB005, CB027, CB058, CB017, CB073, CB028, CB072, CB022, CB008, CB011, CB048, CB002, CB012, CB031, CB057, CB047, CB055, CB041</t>
+          <t>CB023, CB024, CB066, CB014, CB015</t>
         </is>
       </c>
     </row>
@@ -2429,11 +2429,11 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CB041</t>
+          <t>CB029, CB065, CB048, CB020, CB062, CB049, CB013, CB002, CB054</t>
         </is>
       </c>
     </row>
@@ -2470,11 +2470,11 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CB046, CB044</t>
+          <t>CB053, CB014, CB022, CB048, CB010, CB039, CB072, CB007, CB032</t>
         </is>
       </c>
     </row>
@@ -2511,11 +2511,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CB050</t>
+          <t>CB057, CB051, CB053, CB070, CB036</t>
         </is>
       </c>
     </row>
@@ -2552,11 +2552,11 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CB033</t>
+          <t>CB012, CB017, CB046</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CB039</t>
+          <t>CB031</t>
         </is>
       </c>
     </row>
@@ -2634,11 +2634,11 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CB021, CB036, CB048, CB008, CB049, CB023, CB052, CB068, CB022, CB028, CB006, CB027, CB038, CB043</t>
+          <t>CB025, CB056, CB007, CB067, CB011, CB001, CB010, CB065, CB023</t>
         </is>
       </c>
     </row>
@@ -2675,11 +2675,11 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CB047</t>
+          <t>CB063, CB049, CB042, CB071, CB026, CB013, CB039</t>
         </is>
       </c>
     </row>
@@ -2716,11 +2716,11 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CB041, CB046, CB051</t>
+          <t>CB002, CB058</t>
         </is>
       </c>
     </row>
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CB003, CB001, CB029, CB058, CB030, CB043, CB027, CB016, CB039, CB026, CB038, CB067, CB072, CB060, CB054, CB053, CB044, CB034, CB010, CB037, CB049, CB045</t>
+          <t>CB051, CB019, CB073, CB033, CB065, CB040, CB048, CB059</t>
         </is>
       </c>
     </row>
@@ -2798,11 +2798,11 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CB050, CB073, CB041, CB028, CB044, CB052, CB023, CB051, CB013, CB056, CB071, CB005, CB068, CB033, CB012, CB064, CB060, CB014, CB031, CB063, CB022, CB070, CB017, CB004, CB003, CB048, CB066, CB024, CB069, CB062</t>
+          <t>CB064, CB063, CB004, CB020, CB016, CB058, CB047, CB036</t>
         </is>
       </c>
     </row>
@@ -2839,11 +2839,11 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CB040, CB057, CB011, CB049, CB058</t>
+          <t>CB029, CB050, CB027, CB069, CB071, CB013, CB022</t>
         </is>
       </c>
     </row>
@@ -2880,11 +2880,11 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CB013, CB020, CB055, CB007, CB050, CB022, CB030, CB039, CB046, CB016, CB071, CB064, CB072, CB031, CB026, CB040, CB066, CB025, CB034, CB037, CB005, CB015, CB038, CB068, CB035, CB017, CB047, CB010, CB049, CB023, CB070, CB059</t>
+          <t>CB024, CB018</t>
         </is>
       </c>
     </row>
@@ -2921,11 +2921,11 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CB047, CB009, CB062, CB045, CB049, CB073</t>
+          <t>CB040, CB049, CB028, CB020, CB034, CB022, CB014, CB037</t>
         </is>
       </c>
     </row>
@@ -2962,11 +2962,11 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CB014, CB001, CB065, CB008, CB022, CB011, CB041, CB055, CB009, CB036, CB054, CB067, CB052, CB007, CB051, CB004, CB061, CB047, CB006, CB025, CB019, CB035, CB056, CB046, CB039, CB013, CB027, CB023, CB043, CB010, CB034</t>
+          <t>CB050, CB045, CB021, CB071</t>
         </is>
       </c>
     </row>
@@ -3003,11 +3003,11 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CB002, CB069</t>
+          <t>CB016</t>
         </is>
       </c>
     </row>
@@ -3044,11 +3044,11 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CB062, CB034, CB031, CB025, CB042, CB027, CB004, CB066, CB036, CB024, CB065, CB029, CB032, CB028, CB057, CB033, CB005, CB040, CB067, CB021, CB009</t>
+          <t>CB051, CB015, CB062</t>
         </is>
       </c>
     </row>
@@ -3085,11 +3085,11 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CB038</t>
+          <t>CB025, CB055, CB041, CB035, CB019, CB061, CB026</t>
         </is>
       </c>
     </row>
@@ -3126,11 +3126,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CB055, CB006</t>
+          <t>CB046, CB009, CB039</t>
         </is>
       </c>
     </row>
@@ -3167,11 +3167,11 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CB069</t>
+          <t>CB049, CB038, CB064, CB031, CB072, CB052</t>
         </is>
       </c>
     </row>
@@ -3208,11 +3208,11 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CB027, CB023, CB054, CB048, CB007, CB067, CB006, CB028, CB037, CB004, CB011, CB047, CB053, CB057, CB032, CB059, CB049, CB046, CB033, CB044, CB056, CB036, CB024, CB002, CB029, CB012, CB051, CB001, CB005, CB003, CB039</t>
+          <t>CB024, CB073, CB012, CB011, CB025, CB020, CB008</t>
         </is>
       </c>
     </row>
@@ -3249,11 +3249,11 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CB018</t>
+          <t>CB043, CB067, CB016, CB068, CB069, CB007, CB015</t>
         </is>
       </c>
     </row>
@@ -3290,11 +3290,11 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CB025</t>
+          <t>CB032, CB023, CB062, CB033, CB021</t>
         </is>
       </c>
     </row>
@@ -3331,11 +3331,11 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CB055, CB008, CB073</t>
+          <t>CB005</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CB041, CB065, CB059, CB047</t>
+          <t>CB068, CB006, CB022, CB008</t>
         </is>
       </c>
     </row>
@@ -3413,11 +3413,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CB012, CB016</t>
+          <t>CB047</t>
         </is>
       </c>
     </row>
@@ -3454,11 +3454,11 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CB067, CB006, CB029, CB064, CB032, CB049</t>
+          <t>CB028, CB035, CB042, CB048, CB003, CB031, CB025, CB037</t>
         </is>
       </c>
     </row>
@@ -3495,11 +3495,11 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CB007, CB034, CB040, CB014</t>
+          <t>CB045, CB066, CB014, CB055, CB046, CB073</t>
         </is>
       </c>
     </row>
@@ -3536,11 +3536,11 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CB013, CB003, CB063, CB042, CB037, CB043</t>
+          <t>CB030, CB007, CB004, CB062, CB063, CB052, CB059, CB013, CB060</t>
         </is>
       </c>
     </row>
@@ -3577,11 +3577,11 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CB021, CB068, CB029, CB062</t>
+          <t>CB024</t>
         </is>
       </c>
     </row>
@@ -3618,11 +3618,11 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CB048, CB043, CB018, CB054, CB052, CB060</t>
+          <t>CB070</t>
         </is>
       </c>
     </row>
@@ -3659,11 +3659,11 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CB021, CB032, CB012, CB002, CB036, CB046</t>
+          <t>CB066, CB044, CB039, CB057</t>
         </is>
       </c>
     </row>
@@ -3700,11 +3700,11 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CB015, CB050, CB028, CB009</t>
+          <t>CB011, CB035, CB030, CB072, CB059, CB047</t>
         </is>
       </c>
     </row>
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CB011, CB064, CB051, CB047</t>
+          <t>CB069, CB002, CB003, CB073, CB014, CB001, CB044, CB026, CB057</t>
         </is>
       </c>
     </row>
@@ -3821,11 +3821,11 @@
         <v>4.4</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3850,11 +3850,11 @@
         <v>21.4</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3879,11 @@
         <v>6.3</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3908,11 +3908,11 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3937,11 +3937,11 @@
         <v>7.9</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3966,11 @@
         <v>3.8</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -3995,11 +3995,11 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4024,11 +4024,11 @@
         <v>5.3</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4053,11 +4053,11 @@
         <v>2.1</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4082,11 +4082,11 @@
         <v>18.9</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4111,11 +4111,11 @@
         <v>24.4</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
         <v>10.8</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4169,11 +4169,11 @@
         <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4198,11 +4198,11 @@
         <v>24.2</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4227,11 +4227,11 @@
         <v>15.1</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4256,11 +4256,11 @@
         <v>16.6</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4285,11 +4285,11 @@
         <v>9.5</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4314,11 +4314,11 @@
         <v>1.9</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4343,11 +4343,11 @@
         <v>17.7</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4372,11 +4372,11 @@
         <v>14.3</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4401,11 +4401,11 @@
         <v>5.7</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4430,11 +4430,11 @@
         <v>13.9</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4459,11 +4459,11 @@
         <v>23.5</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4488,11 +4488,11 @@
         <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4517,11 +4517,11 @@
         <v>5.8</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4546,11 +4546,11 @@
         <v>22.3</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4575,11 +4575,11 @@
         <v>10.6</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4604,11 +4604,11 @@
         <v>19.5</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4633,11 +4633,11 @@
         <v>6.9</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4662,11 +4662,11 @@
         <v>5.7</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4691,11 +4691,11 @@
         <v>22.2</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4720,11 +4720,11 @@
         <v>11.7</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4749,11 +4749,11 @@
         <v>22.6</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4778,11 +4778,11 @@
         <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4807,11 +4807,11 @@
         <v>12.1</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4836,11 +4836,11 @@
         <v>5.8</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4865,11 @@
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4894,11 +4894,11 @@
         <v>5.4</v>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4923,11 +4923,11 @@
         <v>16.7</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -4952,11 +4952,11 @@
         <v>5.5</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -4981,11 +4981,11 @@
         <v>5.1</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5010,11 +5010,11 @@
         <v>19.8</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5039,11 +5039,11 @@
         <v>23.5</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5068,11 +5068,11 @@
         <v>23.4</v>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5097,11 +5097,11 @@
         <v>23.5</v>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5126,11 +5126,11 @@
         <v>2.6</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5155,11 +5155,11 @@
         <v>23.3</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5184,11 +5184,11 @@
         <v>6.9</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5213,11 +5213,11 @@
         <v>23.7</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5242,11 +5242,11 @@
         <v>14.7</v>
       </c>
       <c r="F51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5271,11 +5271,11 @@
         <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5300,11 +5300,11 @@
         <v>24.7</v>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5329,11 +5329,11 @@
         <v>5.4</v>
       </c>
       <c r="F54" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5358,11 +5358,11 @@
         <v>16</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5387,11 +5387,11 @@
         <v>5.7</v>
       </c>
       <c r="F56" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22/05/2026 - Thứ 6, 22/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>26/05/2026 - Thứ 3, 26/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5416,11 +5416,11 @@
         <v>18</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 27/05/2026 - Thứ 4, 27/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5445,11 +5445,11 @@
         <v>5.7</v>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5474,11 +5474,11 @@
         <v>7.5</v>
       </c>
       <c r="F59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>27/05/2026 - Thứ 4, 27/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 31/05/2026 - Chủ Nhật, 31/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5503,11 +5503,11 @@
         <v>24.8</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5532,11 +5532,11 @@
         <v>10.3</v>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5561,11 +5561,11 @@
         <v>8.9</v>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
+          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5590,11 +5590,11 @@
         <v>21.2</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5619,11 +5619,11 @@
         <v>23.3</v>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5648,11 +5648,11 @@
         <v>16.5</v>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 02/06/2026 - Thứ 3, 02/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5677,11 +5677,11 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19/05/2026 - Thứ 3, 19/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca1 : 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5706,11 +5706,11 @@
         <v>6.7</v>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>23/05/2026 - Thứ 7, 23/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5735,11 +5735,11 @@
         <v>9.5</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2)</t>
+          <t>18/05/2026 - Thứ 2, 18/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5764,11 +5764,11 @@
         <v>10.8</v>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 28/05/2026 - Thứ 5, 28/05/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
+          <t>25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5793,11 +5793,11 @@
         <v>22.7</v>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5822,11 +5822,11 @@
         <v>18.2</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 13/06/2026 - Thứ 7, 13/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2); 09/06/2026 - Thứ 3, 09/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5851,11 +5851,11 @@
         <v>6.2</v>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 10/06/2026 - Thứ 4, 10/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>28/05/2026 - Thứ 5, 28/05/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 4: 15g30-18g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 12/06/2026 - Thứ 6, 12/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5880,11 +5880,11 @@
         <v>17.2</v>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01/06/2026 - Thứ 2, 01/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 09/06/2026 - Thứ 3, 09/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 1: 07g00-09g30 (Cơ sở 1)</t>
+          <t>21/05/2026 - Thứ 5, 21/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 25/05/2026 - Thứ 2, 25/05/2026, Ca 2: 09g30-12g00 (Cơ sở 2); 29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 1); 30/05/2026 - Thứ 7, 30/05/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 4: 15g30-18g00 (Cơ sở 2)</t>
         </is>
       </c>
     </row>
@@ -5909,11 +5909,11 @@
         <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 5: 18g15-20g45 (Cơ sở 1); 01/06/2026 - Thứ 2, 01/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 02/06/2026 - Thứ 3, 02/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 03/06/2026 - Thứ 4, 03/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 04/06/2026 - Thứ 5, 04/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 11/06/2026 - Thứ 5, 11/06/2026, Ca 3: 13g00-15g30 (Cơ sở 2); 12/06/2026 - Thứ 6, 12/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1)</t>
+          <t>29/05/2026 - Thứ 6, 29/05/2026, Ca 1: 07g00-09g30 (Cơ sở 2); 30/05/2026 - Thứ 7, 30/05/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 05/06/2026 - Thứ 6, 05/06/2026, Ca 2: 09g30-12g00 (Cơ sở 1); 08/06/2026 - Thứ 2, 08/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1); 13/06/2026 - Thứ 7, 13/06/2026, Ca 3: 13g00-15g30 (Cơ sở 1)</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>769</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5">
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.5342</v>
+        <v>5.3014</v>
       </c>
     </row>
     <row r="6">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5256</v>
+        <v>0.4589</v>
       </c>
     </row>
   </sheetData>
